--- a/tests/test_results.xlsx
+++ b/tests/test_results.xlsx
@@ -24,20 +24,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
-  <si>
-    <t>image_name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>field</t>
   </si>
   <si>
-    <t>expected_value</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
     <t>chech_01</t>
   </si>
   <si>
@@ -89,26 +80,35 @@
     <t>بانک سامان</t>
   </si>
   <si>
-    <t>موسسه فرهنگی ورزشی رزمی</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
     <t>pass</t>
   </si>
   <si>
     <t>fail</t>
   </si>
   <si>
-    <t>processing_time_ms</t>
+    <t>Expected Value</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>8601040043556490</t>
+  </si>
+  <si>
+    <t>86010400435564902</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +134,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="B Nazanin"/>
+      <charset val="178"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -155,9 +169,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -170,16 +183,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -190,6 +252,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:F13" totalsRowShown="0">
+  <autoFilter ref="A2:F13"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="chech_01" dataDxfId="2"/>
+    <tableColumn id="2" name="sayad_id"/>
+    <tableColumn id="3" name="8601040043556490" dataDxfId="1"/>
+    <tableColumn id="4" name="86010400435564902"/>
+    <tableColumn id="5" name="pass" dataDxfId="0"/>
+    <tableColumn id="6" name="Column1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13.05078125" customWidth="1"/>
@@ -463,187 +540,190 @@
     <col min="3" max="3" width="41.41796875" customWidth="1"/>
     <col min="4" max="4" width="45.3671875" customWidth="1"/>
     <col min="5" max="5" width="12.9453125" customWidth="1"/>
+    <col min="6" max="6" width="9.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4"/>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5" t="s">
+      <c r="C3" s="2">
+        <v>300000000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>300000000</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.100000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3">
-        <v>8601040043556490</v>
-      </c>
-      <c r="D2" s="3">
-        <v>8601040043556490</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6" t="s">
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.100000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3">
-        <v>300000000</v>
-      </c>
-      <c r="D3" s="3">
-        <v>300000000</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6" t="s">
+      <c r="C6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.100000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6" t="s">
+      <c r="C7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C8" s="2">
+        <v>5608216</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5608216</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3">
-        <v>5608216</v>
-      </c>
-      <c r="D8" s="3">
-        <v>5608216</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5"/>
-      <c r="B11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="7">
-        <v>54979</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C14" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>